--- a/reports/pdf_rolling5_20260910.xlsx
+++ b/reports/pdf_rolling5_20260910.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,482억   ·   현금 31억(0.7%)      오늘 2026-09-10  vs  5일전 2026-09-03      매수 16종목  /  매도 14종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,595억   ·   현금 15억(0.3%)      오늘 2026-09-10  vs  5일전 2026-09-03      매수 16종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>935</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>6292035750</v>
+        <v>6273438600</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-70</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1598625000</v>
+        <v>-1593900000</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>116</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>445057200</v>
+        <v>443741760</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-46</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-3272969000</v>
+        <v>-3263295200</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>109</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1301067600</v>
+        <v>1297222080</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-40</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-3045000000</v>
+        <v>-3036000000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>42</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1619940000</v>
+        <v>1615152000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-34</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1207850000</v>
+        <v>-1204280000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>40</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1266720000</v>
+        <v>1262976000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-34</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-9645545000</v>
+        <v>-9617036000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>39</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>461165250</v>
+        <v>459802200</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-28</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-8810200000</v>
+        <v>-8784160000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>34</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>5259324000</v>
+        <v>5243779200</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-24</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-884268000</v>
+        <v>-881654400</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>32</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1401512000</v>
+        <v>1397369600</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-21</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-931465500</v>
+        <v>-928712400</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>28</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>917966000</v>
+        <v>915252800</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>-18</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-904365000</v>
+        <v>-901692000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>27</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1362028500</v>
+        <v>1358002800</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>-14</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1884246000</v>
+        <v>-1878676800</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>26</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>953998500</v>
+        <v>951178800</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>-12</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-840420000</v>
+        <v>-837936000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>23</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>10972150000</v>
+        <v>10939720000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>-9</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-824890500</v>
+        <v>-822452400</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>21</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1481392500</v>
+        <v>1477014000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>-8</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-462028000</v>
+        <v>-460662400</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>20</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>980490000</v>
+        <v>977592000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>-3</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-469843500</v>
+        <v>-468454800</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>12</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1172934000</v>
+        <v>1169467200</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>3</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>784087500</v>
+        <v>781770000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,518억   ·   현금 87억(2.4%)      오늘 2026-09-10  vs  5일전 2026-09-03      매수 4종목  /  매도 5종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,531억   ·   현금 44억(1.2%)      오늘 2026-09-10  vs  5일전 2026-09-03      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -1628,7 +1628,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,521억   ·   현금 70억(2.6%)      오늘 2026-09-10  vs  5일전 2026-09-03      매수 8종목  /  매도 8종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,613억   ·   현금 35억(1.3%)      오늘 2026-09-10  vs  5일전 2026-09-03      매수 8종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1724,7 +1724,7 @@
         <v>396</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>2284860600</v>
+        <v>2278247400</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>-214</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-2933820160</v>
+        <v>-2925328640</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>59</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>3803747700</v>
+        <v>3792738300</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>-149</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-2151843100</v>
+        <v>-2145614900</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>36</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>1118176200</v>
+        <v>1114939800</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>-96</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-8796153600</v>
+        <v>-8770694400</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>24</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>2558911200</v>
+        <v>2551504800</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>-71</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-1101419450</v>
+        <v>-1098231550</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>18</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>621278100</v>
+        <v>619479900</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>-65</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-2043632500</v>
+        <v>-2037717500</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>15</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3213150000</v>
+        <v>3203850000</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>-62</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-1430922800</v>
+        <v>-1426781200</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>15</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>2783002500</v>
+        <v>2774947500</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>-50</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-1641125000</v>
+        <v>-1636375000</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>13</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>4222010000</v>
+        <v>4209790000</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>-29</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-1364655900</v>
+        <v>-1360706100</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
     <row r="44" ht="19" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,991억   ·   현금 5억(0.2%)      오늘 2026-09-10  vs  5일전 2026-09-03      매수 6종목  /  매도 9종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,000억   ·   현금 2억(0.1%)      오늘 2026-09-10  vs  5일전 2026-09-03      매수 6종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B44" s="4" t="n"/>
@@ -2506,7 +2506,7 @@
     <row r="57" ht="19" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 270억   ·   현금 2억(0.9%)      오늘 2026-09-10  vs  5일전 2026-09-03      매수 9종목  /  매도 10종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 280억   ·   현금 1억(0.4%)      오늘 2026-09-10  vs  5일전 2026-09-03      매수 9종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B57" s="4" t="n"/>
@@ -2602,11 +2602,11 @@
         <v>274</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>178374000</v>
+        <v>192567200</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>6.56%→7.23%</t>
+          <t>6.83%→7.52%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -2623,11 +2623,11 @@
         <v>-105</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-167580000</v>
+        <v>-170520000</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>5.79%→5.17%</t>
+          <t>5.68%→5.07%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
@@ -2646,11 +2646,11 @@
         <v>47</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>58298800</v>
+        <v>57377600</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>3.59%→3.81%</t>
+          <t>3.41%→3.61%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
@@ -2667,11 +2667,11 @@
         <v>-93</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-66011400</v>
+        <v>-70373100</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>1.05%→0.80%</t>
+          <t>1.08%→0.83%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
@@ -2690,11 +2690,11 @@
         <v>26</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>37401000</v>
+        <v>40131000</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>1.57%→1.71%</t>
+          <t>1.62%→1.77%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
@@ -2711,11 +2711,11 @@
         <v>-38</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-109725000</v>
+        <v>-119567000</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>4.02%→3.62%</t>
+          <t>4.23%→3.80%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
@@ -2734,11 +2734,11 @@
         <v>25</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>61250000</v>
+        <v>63700000</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>7.09%→7.32%</t>
+          <t>7.11%→7.34%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
@@ -2755,11 +2755,11 @@
         <v>-18</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-52038000</v>
+        <v>-54369000</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>2.76%→2.56%</t>
+          <t>2.78%→2.58%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
@@ -2778,11 +2778,11 @@
         <v>23</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>82754000</v>
+        <v>83881000</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>1.02%→1.33%</t>
+          <t>1.00%→1.30%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
@@ -2799,11 +2799,11 @@
         <v>-17</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-74018000</v>
+        <v>-82705000</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>1.83%→1.56%</t>
+          <t>1.97%→1.68%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
@@ -2822,11 +2822,11 @@
         <v>21</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>67987500</v>
+        <v>65562000</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>0.95%→1.21%</t>
+          <t>0.89%→1.12%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
@@ -2843,11 +2843,11 @@
         <v>-9</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-23814000</v>
+        <v>-22396500</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>1.09%→1.01%</t>
+          <t>0.99%→0.91%</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
@@ -2866,7 +2866,7 @@
         <v>14</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>69874000</v>
+        <v>72226000</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
@@ -2887,11 +2887,11 @@
         <v>-6</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-21462000</v>
+        <v>-20832000</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
-          <t>2.92%→2.84%</t>
+          <t>2.73%→2.66%</t>
         </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
@@ -2910,11 +2910,11 @@
         <v>4</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>23268000</v>
+        <v>24472000</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>1.71%→1.80%</t>
+          <t>1.74%→1.82%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
@@ -2931,11 +2931,11 @@
         <v>-6</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-61530000</v>
+        <v>-64008000</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>3.71%→3.48%</t>
+          <t>3.72%→3.49%</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
@@ -2954,11 +2954,11 @@
         <v>3</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>93765000</v>
+        <v>98700000</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>0.82%→1.16%</t>
+          <t>0.83%→1.18%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
@@ -2975,11 +2975,11 @@
         <v>-5</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-44135000</v>
+        <v>-43260000</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>0.36%→0.20%</t>
+          <t>0.34%→0.19%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
@@ -3003,11 +3003,11 @@
         <v>-3</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-77490000</v>
+        <v>-76860000</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>0.29%→0.00%</t>
+          <t>0.28%→0.00%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
@@ -3019,7 +3019,7 @@
     <row r="71" ht="19" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 498억   ·   현금 8억(1.7%)      오늘 2026-09-10  vs  5일전 2026-09-03      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 500억   ·   현금 4억(0.8%)      오늘 2026-09-10  vs  5일전 2026-09-03      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B71" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260910.xlsx
+++ b/reports/pdf_rolling5_20260910.xlsx
@@ -2223,23 +2223,23 @@
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>보로노이</t>
+          <t>지아이이노베이션  (편출)</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
         <v>-119</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-5876684100</v>
+        <v>-320978700</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>6.86%→3.16%</t>
+          <t>0.16%→0.00%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>247→128</t>
+          <t>119→0</t>
         </is>
       </c>
     </row>
@@ -2267,23 +2267,23 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>지아이이노베이션  (편출)</t>
+          <t>보로노이</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-119</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-320978700</v>
+        <v>-5876684100</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.16%→0.00%</t>
+          <t>6.86%→3.16%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>119→0</t>
+          <t>247→128</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260910.xlsx
+++ b/reports/pdf_rolling5_20260910.xlsx
@@ -816,23 +816,23 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1204280000</v>
+        <v>-9617036000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.60%→0.28%</t>
+          <t>6.72%→3.86%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>70→36</t>
+          <t>97→63</t>
         </is>
       </c>
     </row>
@@ -860,23 +860,23 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-9617036000</v>
+        <v>-1204280000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>6.72%→3.86%</t>
+          <t>0.60%→0.28%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>97→63</t>
+          <t>70→36</t>
         </is>
       </c>
     </row>
@@ -1937,23 +1937,23 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>로보티즈  (신규)</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B40" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3203850000</v>
+        <v>2774947500</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.24%</t>
+          <t>2.33%→3.58%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>0→15</t>
+          <t>35→50</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -1981,23 +1981,23 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>로보티즈  (신규)</t>
         </is>
       </c>
       <c r="B41" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>2774947500</v>
+        <v>3203850000</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>2.33%→3.58%</t>
+          <t>0.00%→1.24%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>35→50</t>
+          <t>0→15</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260910.xlsx
+++ b/reports/pdf_rolling5_20260910.xlsx
@@ -816,23 +816,23 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-9617036000</v>
+        <v>-1204280000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>6.72%→3.86%</t>
+          <t>0.60%→0.28%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>97→63</t>
+          <t>70→36</t>
         </is>
       </c>
     </row>
@@ -860,23 +860,23 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1204280000</v>
+        <v>-9617036000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.60%→0.28%</t>
+          <t>6.72%→3.86%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>70→36</t>
+          <t>97→63</t>
         </is>
       </c>
     </row>
@@ -1937,23 +1937,23 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>로보티즈  (신규)</t>
         </is>
       </c>
       <c r="B40" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>2774947500</v>
+        <v>3203850000</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>2.33%→3.58%</t>
+          <t>0.00%→1.24%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>35→50</t>
+          <t>0→15</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -1981,23 +1981,23 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>로보티즈  (신규)</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B41" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>3203850000</v>
+        <v>2774947500</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.24%</t>
+          <t>2.33%→3.58%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>0→15</t>
+          <t>35→50</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
@@ -2223,23 +2223,23 @@
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>지아이이노베이션  (편출)</t>
+          <t>보로노이</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
         <v>-119</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-320978700</v>
+        <v>-5876684100</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>0.16%→0.00%</t>
+          <t>6.86%→3.16%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>119→0</t>
+          <t>247→128</t>
         </is>
       </c>
     </row>
@@ -2267,23 +2267,23 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>보로노이</t>
+          <t>지아이이노베이션  (편출)</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-119</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-5876684100</v>
+        <v>-320978700</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>6.86%→3.16%</t>
+          <t>0.16%→0.00%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>247→128</t>
+          <t>119→0</t>
         </is>
       </c>
     </row>
@@ -2880,23 +2880,23 @@
       </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H66" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-20832000</v>
+        <v>-64008000</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
-          <t>2.73%→2.66%</t>
+          <t>3.72%→3.49%</t>
         </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
         <is>
-          <t>219→213</t>
+          <t>97→91</t>
         </is>
       </c>
     </row>
@@ -2924,23 +2924,23 @@
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H67" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-64008000</v>
+        <v>-20832000</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>3.72%→3.49%</t>
+          <t>2.73%→2.66%</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
         <is>
-          <t>97→91</t>
+          <t>219→213</t>
         </is>
       </c>
     </row>
